--- a/artfynd/A 42123-2024 artfynd.xlsx
+++ b/artfynd/A 42123-2024 artfynd.xlsx
@@ -8711,10 +8711,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121098683</v>
+        <v>121091584</v>
       </c>
       <c r="B67" t="n">
-        <v>57976</v>
+        <v>57351</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8723,20 +8723,20 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>102125</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -8744,16 +8744,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -8763,10 +8759,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>728123</v>
+        <v>728177</v>
       </c>
       <c r="R67" t="n">
-        <v>7082601</v>
+        <v>7082621</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8799,6 +8795,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-11-08</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8825,10 +8826,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121091584</v>
+        <v>121098683</v>
       </c>
       <c r="B68" t="n">
-        <v>57348</v>
+        <v>57979</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8837,20 +8838,20 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>102125</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -8858,12 +8859,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -8873,10 +8878,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>728177</v>
+        <v>728123</v>
       </c>
       <c r="R68" t="n">
-        <v>7082621</v>
+        <v>7082601</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8909,11 +8914,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-11-08</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD68" t="b">

--- a/artfynd/A 42123-2024 artfynd.xlsx
+++ b/artfynd/A 42123-2024 artfynd.xlsx
@@ -8711,10 +8711,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121091584</v>
+        <v>121098683</v>
       </c>
       <c r="B67" t="n">
-        <v>57351</v>
+        <v>57979</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8723,20 +8723,20 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>102125</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -8744,12 +8744,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -8759,10 +8763,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>728177</v>
+        <v>728123</v>
       </c>
       <c r="R67" t="n">
-        <v>7082621</v>
+        <v>7082601</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8795,11 +8799,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-11-08</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8826,10 +8825,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121098683</v>
+        <v>121091584</v>
       </c>
       <c r="B68" t="n">
-        <v>57979</v>
+        <v>57351</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8838,20 +8837,20 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>102125</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -8859,16 +8858,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -8878,10 +8873,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>728123</v>
+        <v>728177</v>
       </c>
       <c r="R68" t="n">
-        <v>7082601</v>
+        <v>7082621</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8914,6 +8909,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-11-08</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD68" t="b">

--- a/artfynd/A 42123-2024 artfynd.xlsx
+++ b/artfynd/A 42123-2024 artfynd.xlsx
@@ -8711,10 +8711,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121098683</v>
+        <v>121091584</v>
       </c>
       <c r="B67" t="n">
-        <v>57979</v>
+        <v>57351</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8723,20 +8723,20 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>102125</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -8744,16 +8744,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -8763,10 +8759,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>728123</v>
+        <v>728177</v>
       </c>
       <c r="R67" t="n">
-        <v>7082601</v>
+        <v>7082621</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8799,6 +8795,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-11-08</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8825,10 +8826,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121091584</v>
+        <v>121098683</v>
       </c>
       <c r="B68" t="n">
-        <v>57351</v>
+        <v>57979</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8837,20 +8838,20 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>102125</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -8858,12 +8859,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -8873,10 +8878,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>728177</v>
+        <v>728123</v>
       </c>
       <c r="R68" t="n">
-        <v>7082621</v>
+        <v>7082601</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8909,11 +8914,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-11-08</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD68" t="b">

--- a/artfynd/A 42123-2024 artfynd.xlsx
+++ b/artfynd/A 42123-2024 artfynd.xlsx
@@ -8714,7 +8714,7 @@
         <v>121091584</v>
       </c>
       <c r="B67" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         <v>121098683</v>
       </c>
       <c r="B68" t="n">
-        <v>57979</v>
+        <v>57982</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
